--- a/out/thesis/tables/hypotheses_significance_map_ru.xlsx
+++ b/out/thesis/tables/hypotheses_significance_map_ru.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="84">
   <si>
     <t>Гипотеза</t>
   </si>
@@ -97,6 +97,9 @@
     <t>H22</t>
   </si>
   <si>
+    <t>H23</t>
+  </si>
+  <si>
     <t>Мгновенная внутридневная реакция</t>
   </si>
   <si>
@@ -151,7 +154,7 @@
     <t>Связь CAR короткого окна и BHAR</t>
   </si>
   <si>
-    <t>Пост-сделочный дрейф BHAR</t>
+    <t>Долгосрочный BHAR (+1;+120) после объявления не положителен (отрицательный пост-сделочный дрейф)</t>
   </si>
   <si>
     <t>Ecosystem vs non-ecosystem BHAR</t>
@@ -163,6 +166,9 @@
     <t>Пост-сделочные финансы (прочее)</t>
   </si>
   <si>
+    <t>Долгосрочный BHAR (+1;+250) не положителен</t>
+  </si>
+  <si>
     <t>CAR_ANN_INTRADAY_15M</t>
   </si>
   <si>
@@ -218,6 +224,9 @@
   </si>
   <si>
     <t>требуются данные</t>
+  </si>
+  <si>
+    <t>BHAR_ANN_250</t>
   </si>
   <si>
     <t>НЕТ</t>
@@ -588,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -613,16 +622,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -630,16 +639,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -647,16 +656,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -664,13 +673,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -678,16 +687,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -695,16 +704,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -712,16 +721,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -729,16 +738,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -746,16 +755,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -763,13 +772,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -777,13 +786,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -791,13 +800,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -805,13 +814,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -819,16 +828,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -836,16 +845,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -853,16 +862,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -870,16 +879,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -887,13 +896,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -901,13 +910,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -915,13 +924,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -929,16 +938,16 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -946,15 +955,29 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" t="s">
         <v>72</v>
       </c>
     </row>
